--- a/BOM_M2_Mosaic-G5_Smart_REV_01.01_VARIANT_Mosaic-G5_P6H.xlsx
+++ b/BOM_M2_Mosaic-G5_Smart_REV_01.01_VARIANT_Mosaic-G5_P6H.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\M2_Mosaic-G5_Smart\Project Outputs for M2_Mosaic-G5_Smart\Assembly\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://septentrio-my.sharepoint.com/personal/laetitia_kazingufu-furaha_septentrio_com/Documents/Documents/GitHub/MosaicM2G5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90B0780A-790E-460F-90C4-BFBB9720EE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{90B0780A-790E-460F-90C4-BFBB9720EE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F29957E-89EF-43FE-BED7-4605EDE2E7AE}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="780" windowWidth="21600" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36540" yWindow="2412" windowWidth="14400" windowHeight="8172" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>Bill of Materials</t>
   </si>
@@ -97,9 +97,6 @@
     <t>NTK3043NT1G</t>
   </si>
   <si>
-    <t>mosaic-G5-P6H</t>
-  </si>
-  <si>
     <t>PCB</t>
   </si>
   <si>
@@ -200,6 +197,16 @@
   </si>
   <si>
     <t>863-NTK3043NT1G</t>
+  </si>
+  <si>
+    <t>mosaic-G5-P3H</t>
+  </si>
+  <si>
+    <t>Septentrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+410502</t>
   </si>
 </sst>
 </file>
@@ -403,8 +410,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{65D0A34F-38EA-470E-BF9B-CC9F9FF7C0E3}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -494,6 +501,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -760,15 +771,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="9" width="30.7109375" customWidth="1"/>
+    <col min="2" max="4" width="30.7265625" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" customWidth="1"/>
+    <col min="6" max="9" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:10" ht="30" x14ac:dyDescent="0.35">
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
         <v>0</v>
@@ -781,11 +792,11 @@
       <c r="I2" s="3"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
         <v>1</v>
@@ -799,7 +810,7 @@
       </c>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
         <v>3</v>
@@ -813,7 +824,7 @@
       </c>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
         <v>5</v>
@@ -827,7 +838,7 @@
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
         <v>7</v>
@@ -843,208 +854,214 @@
       </c>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="4"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>39</v>
-      </c>
       <c r="G11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="I11" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="15">
         <v>1</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="15">
         <v>1</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="15">
         <v>6</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" s="15">
         <v>3</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="15">
         <v>2</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>19</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="2:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>20</v>
-      </c>
       <c r="C17" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="15">
         <v>1</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="F17" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="I17" s="14"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" s="15">
         <v>1</v>
@@ -1055,7 +1072,7 @@
       <c r="I18" s="14"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" ht="30" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="2"/>
       <c r="D19" s="3"/>
